--- a/src/assets/mismatch_report.xlsx
+++ b/src/assets/mismatch_report.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myl-my.sharepoint.com/personal/aditya_ambaldhage_viatris_com/Documents/Desktop/Consistency Result Sheet - Copy/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M685844\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{64797B07-6F4B-44A3-BE92-6BFFDED12091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B73E2C0-431F-4C06-971F-9494D893C1B0}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09961041-616A-4694-8B5B-EE3F62E76E94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,36 +16,20 @@
     <sheet name="Mismatch Summary" sheetId="1" r:id="rId1"/>
     <sheet name="All Mismatch Rows" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="99">
   <si>
     <t>Cross-Document Statistical Value Mismatch Report by Cluster</t>
   </si>
   <si>
-    <t>Same parameter + sub-parameter + group + timepoint in multiple documents — documents disagree on the value or unit</t>
-  </si>
-  <si>
-    <t>Mismatch clusters: 13   |   Rows involved: 28   |   Value mismatches: 13   |   Unit mismatches: 0   |   Both: 0   |   Unique documents: 5</t>
+    <t>Same parameter + sub-parameter + group in multiple documents — documents disagree on the value or unit</t>
+  </si>
+  <si>
+    <t>Mismatch clusters: 8   |   Rows involved: 28   |   Value mismatches: 8   |   Unit mismatches: 0   |   Both: 0   |   Unique documents: 8</t>
   </si>
   <si>
     <t xml:space="preserve">  Treatment-emergent adverse events    (2 rows)   ⚠ value mismatch</t>
@@ -120,64 +104,175 @@
     <t>2.5-clinical-overview.pdf</t>
   </si>
   <si>
+    <t xml:space="preserve">  Tablet strength inconsistency    (2 rows)   ⚠ value mismatch</t>
+  </si>
+  <si>
+    <t>Tablet Strength</t>
+  </si>
+  <si>
     <t>Nexivarin Hydrochloride</t>
   </si>
   <si>
+    <t>Synopsis</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>mg</t>
   </si>
   <si>
-    <t xml:space="preserve"> Headache incidence discrepancy    (2 rows)   ⚠ value mismatch</t>
-  </si>
-  <si>
-    <t>Headache</t>
+    <t>2.3.P</t>
+  </si>
+  <si>
+    <t>Drug Product</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>2.3-qos.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Dose Levels discrepancy    (2 rows)   ⚠ value mismatch</t>
+  </si>
+  <si>
+    <t>Dose Levels</t>
+  </si>
+  <si>
+    <t>NOAEL</t>
+  </si>
+  <si>
+    <t>4.2.3.2</t>
+  </si>
+  <si>
+    <t>Repeat-Dose Toxicity Studies</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>mg/kg/day</t>
+  </si>
+  <si>
+    <t>4.2.3.2-repeat-dose-tox</t>
+  </si>
+  <si>
+    <t>2.4.4</t>
+  </si>
+  <si>
+    <t>Repeat-Dose Toxicity</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>2.4-nonclinical-overview</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Adverse event: pKa   (2 rows)   ⚠ value mismatch</t>
+  </si>
+  <si>
+    <t>pKa</t>
+  </si>
+  <si>
+    <t>3.2.S.1.3</t>
+  </si>
+  <si>
+    <t>General Properties</t>
+  </si>
+  <si>
+    <t>9.4</t>
+  </si>
+  <si>
+    <t>3.2.S.1-general-info</t>
+  </si>
+  <si>
+    <t>2.3.S.1</t>
+  </si>
+  <si>
+    <t>General Information</t>
+  </si>
+  <si>
+    <t>7.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Dizziness adverse event frequency    (2 rows)   ⚠ value mismatch</t>
+  </si>
+  <si>
+    <t>Dizziness</t>
   </si>
   <si>
     <t>Placebo</t>
   </si>
   <si>
-    <t>7.6</t>
-  </si>
-  <si>
-    <t>7.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Adverse event: dizziness    (2 rows)   ⚠ value mismatch</t>
-  </si>
-  <si>
-    <t>Dizziness</t>
-  </si>
-  <si>
-    <t>3.1</t>
-  </si>
-  <si>
-    <t>3.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Dizziness adverse event frequency    (2 rows)   ⚠ value mismatch</t>
-  </si>
-  <si>
     <t>1.3</t>
   </si>
   <si>
     <t>1.5</t>
   </si>
   <si>
-    <t xml:space="preserve">  Adverse event: headache frequency    (2 rows)   ⚠ value mismatch</t>
-  </si>
-  <si>
-    <t>7.1</t>
-  </si>
-  <si>
-    <t>7.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Treatment-emergent adverse events    (2 rows)   ⚠ value mismatch</t>
-  </si>
-  <si>
-    <t>50.1</t>
-  </si>
-  <si>
-    <t>52.8</t>
+    <t xml:space="preserve"> Human coronary artery SMC adverse events    (2 rows)   ⚠ value mismatch</t>
+  </si>
+  <si>
+    <t>Human coronary artery SMC</t>
+  </si>
+  <si>
+    <t>IC50</t>
+  </si>
+  <si>
+    <t>4.2.1.1</t>
+  </si>
+  <si>
+    <t>Primary Pharmacodynamics — Nexivarin Hydrochloride</t>
+  </si>
+  <si>
+    <t>2.3 ± 0.4</t>
+  </si>
+  <si>
+    <t>(nM)</t>
+  </si>
+  <si>
+    <t>4.2.1.1-primary-pd</t>
+  </si>
+  <si>
+    <t>2.4.2</t>
+  </si>
+  <si>
+    <t>Pharmacology</t>
+  </si>
+  <si>
+    <t>2.7 ± 0.1</t>
+  </si>
+  <si>
+    <t>2.4-nonclinical-overview.pdf</t>
+  </si>
+  <si>
+    <t>hERG IC50 inconsistency  (2 rows)   ⚠ value mismatch</t>
+  </si>
+  <si>
+    <t>hERG IC50</t>
+  </si>
+  <si>
+    <t>safety margin</t>
+  </si>
+  <si>
+    <t>4.2.1.3</t>
+  </si>
+  <si>
+    <t>Safety Pharmacology — Nexivarin Hydrochloride</t>
+  </si>
+  <si>
+    <t>10,000</t>
+  </si>
+  <si>
+    <t>nM</t>
+  </si>
+  <si>
+    <t>4.2.1.3-safety-pharm.pdf</t>
+  </si>
+  <si>
+    <t>Safety Pharmacology</t>
   </si>
   <si>
     <t xml:space="preserve">  Adverse event: flushing    (2 rows)   ⚠ value mismatch</t>
@@ -186,12 +281,6 @@
     <t>Flushing</t>
   </si>
   <si>
-    <t>0.4</t>
-  </si>
-  <si>
-    <t>0.5</t>
-  </si>
-  <si>
     <t>2.4</t>
   </si>
   <si>
@@ -229,28 +318,13 @@
   </si>
   <si>
     <t>mismatch_type</t>
-  </si>
-  <si>
-    <t>Dose mismatch across studies    (2 rows)   ⚠ value + unit mismatch</t>
-  </si>
-  <si>
-    <t>Dose</t>
-  </si>
-  <si>
-    <t>4.2.3.2-repeat-dose-tox.pdf</t>
-  </si>
-  <si>
-    <t>4.2.3.2</t>
-  </si>
-  <si>
-    <t>Repeat-Dose Toxicity Studies</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -323,6 +397,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF2C2C2A"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -364,7 +444,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -417,14 +497,38 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="3"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -450,11 +554,23 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="2" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="3" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="3" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="3" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -769,77 +885,77 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="32" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="28" customWidth="1"/>
-    <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="8" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="36" customWidth="1"/>
-    <col min="10" max="10" width="18" customWidth="1"/>
+    <col min="1" max="1" width="32" style="11" customWidth="1"/>
+    <col min="2" max="2" width="30" style="11" customWidth="1"/>
+    <col min="3" max="3" width="14" style="11" customWidth="1"/>
+    <col min="4" max="4" width="28" style="11" customWidth="1"/>
+    <col min="5" max="5" width="13" style="11" customWidth="1"/>
+    <col min="6" max="6" width="16" style="11" customWidth="1"/>
+    <col min="7" max="7" width="11" style="11" customWidth="1"/>
+    <col min="8" max="8" width="10" style="11" customWidth="1"/>
+    <col min="9" max="9" width="36" style="11" customWidth="1"/>
+    <col min="10" max="10" width="18" style="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
     </row>
     <row r="3" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
     </row>
     <row r="4" spans="1:10" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="5" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="17"/>
     </row>
     <row r="6" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
@@ -919,7 +1035,7 @@
         <v>24</v>
       </c>
       <c r="E8" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>25</v>
@@ -939,18 +1055,18 @@
     </row>
     <row r="9" spans="1:10" ht="4" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="10" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="11"/>
+      <c r="A10" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="17"/>
     </row>
     <row r="11" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="8" t="s">
@@ -985,32 +1101,32 @@
       </c>
     </row>
     <row r="12" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="1" t="s">
-        <v>65</v>
+      <c r="A12" s="9" t="s">
+        <v>28</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>67</v>
+        <v>16</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="E12" s="1">
         <v>3</v>
       </c>
-      <c r="F12" s="7">
-        <v>30</v>
+      <c r="F12" s="7" t="s">
+        <v>31</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>66</v>
+        <v>21</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>22</v>
@@ -1018,31 +1134,31 @@
     </row>
     <row r="13" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>67</v>
+        <v>33</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="E13" s="1">
-        <v>3</v>
-      </c>
-      <c r="F13" s="7">
+        <v>5</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>22</v>
@@ -1050,18 +1166,18 @@
     </row>
     <row r="14" spans="1:10" ht="4" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="15" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
+      <c r="A15" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="17"/>
     </row>
     <row r="16" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="8" t="s">
@@ -1097,31 +1213,31 @@
     </row>
     <row r="17" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="E17" s="1">
-        <v>4</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>32</v>
+        <v>3</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>42</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>22</v>
@@ -1129,102 +1245,133 @@
     </row>
     <row r="18" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="E18" s="1">
         <v>4</v>
       </c>
-      <c r="F18" s="7" t="s">
-        <v>33</v>
+      <c r="F18" s="10" t="s">
+        <v>47</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="4" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="1:10" ht="4" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="21" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="11"/>
-      <c r="J21" s="11"/>
-    </row>
-    <row r="22" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="8" t="s">
+    <row r="20" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" s="16"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="16"/>
+      <c r="I20" s="16"/>
+      <c r="J20" s="17"/>
+    </row>
+    <row r="21" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B21" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C21" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D21" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E22" s="8" t="s">
+      <c r="E21" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F22" s="8" t="s">
+      <c r="F21" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G22" s="8" t="s">
+      <c r="G21" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H22" s="8" t="s">
+      <c r="H21" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="I22" s="8" t="s">
+      <c r="I21" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="J22" s="8" t="s">
+      <c r="J21" s="8" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E22" s="1">
+        <v>4</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="E23" s="1">
-        <v>4</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>36</v>
+        <v>3</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>53</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>19</v>
@@ -1233,109 +1380,109 @@
         <v>20</v>
       </c>
       <c r="I23" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="4" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="25" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="16"/>
+      <c r="H25" s="16"/>
+      <c r="I25" s="16"/>
+      <c r="J25" s="17"/>
+    </row>
+    <row r="26" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J26" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E27" s="1">
+        <v>2</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I27" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E24" s="1">
-        <v>4</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="4" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="26" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="11"/>
-      <c r="I26" s="11"/>
-      <c r="J26" s="11"/>
-    </row>
-    <row r="27" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G27" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="H27" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="I27" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="J27" s="8" t="s">
-        <v>13</v>
+      <c r="J27" s="3" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E28" s="1">
         <v>4</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>19</v>
@@ -1344,331 +1491,331 @@
         <v>20</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J28" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E29" s="1">
+    <row r="29" spans="1:10" ht="4" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="30" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="B30" s="16"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="16"/>
+      <c r="H30" s="16"/>
+      <c r="I30" s="16"/>
+      <c r="J30" s="17"/>
+    </row>
+    <row r="31" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F29" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H29" s="2" t="s">
+      <c r="B31" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="I31" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J31" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E32" s="1">
+        <v>4</v>
+      </c>
+      <c r="F32" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H32" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I29" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="4" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="31" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="B31" s="11"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="11"/>
-      <c r="H31" s="11"/>
-      <c r="I31" s="11"/>
-      <c r="J31" s="11"/>
-    </row>
-    <row r="32" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G32" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="H32" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="I32" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="J32" s="8" t="s">
-        <v>13</v>
+      <c r="I32" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>16</v>
+        <v>71</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="E33" s="1">
-        <v>4</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>42</v>
+        <v>3</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>73</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>21</v>
+        <v>74</v>
       </c>
       <c r="J33" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E34" s="1">
+    <row r="34" spans="1:10" ht="4" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="35" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
+      <c r="H35" s="16"/>
+      <c r="I35" s="16"/>
+      <c r="J35" s="17"/>
+    </row>
+    <row r="36" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F34" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H34" s="2" t="s">
+      <c r="B36" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H36" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="I36" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J36" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E37" s="1">
+        <v>2</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H37" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I34" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" ht="4" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="36" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="B36" s="11"/>
-      <c r="C36" s="11"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="11"/>
-      <c r="H36" s="11"/>
-      <c r="I36" s="11"/>
-      <c r="J36" s="11"/>
-    </row>
-    <row r="37" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B37" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D37" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F37" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G37" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="H37" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="I37" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="J37" s="8" t="s">
-        <v>13</v>
+      <c r="I37" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="B38" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E38" s="1">
+        <v>3</v>
+      </c>
+      <c r="F38" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C38" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E38" s="1">
-        <v>4</v>
-      </c>
-      <c r="F38" s="7" t="s">
-        <v>45</v>
-      </c>
       <c r="G38" s="1" t="s">
-        <v>19</v>
+        <v>81</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I38" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="4" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="40" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B40" s="16"/>
+      <c r="C40" s="16"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="16"/>
+      <c r="F40" s="16"/>
+      <c r="G40" s="16"/>
+      <c r="H40" s="16"/>
+      <c r="I40" s="16"/>
+      <c r="J40" s="17"/>
+    </row>
+    <row r="41" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G41" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H41" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="I41" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J41" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E42" s="1">
+        <v>2</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I42" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="J38" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E39" s="1">
-        <v>4</v>
-      </c>
-      <c r="F39" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I39" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="4" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="41" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="B41" s="11"/>
-      <c r="C41" s="11"/>
-      <c r="D41" s="11"/>
-      <c r="E41" s="11"/>
-      <c r="F41" s="11"/>
-      <c r="G41" s="11"/>
-      <c r="H41" s="11"/>
-      <c r="I41" s="11"/>
-      <c r="J41" s="11"/>
-    </row>
-    <row r="42" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B42" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D42" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F42" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G42" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="H42" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="I42" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="J42" s="8" t="s">
-        <v>13</v>
+      <c r="J42" s="3" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E43" s="1">
         <v>4</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>19</v>
@@ -1677,170 +1824,26 @@
         <v>20</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E44" s="1">
-        <v>4</v>
-      </c>
-      <c r="F44" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" ht="4" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="46" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="B46" s="11"/>
-      <c r="C46" s="11"/>
-      <c r="D46" s="11"/>
-      <c r="E46" s="11"/>
-      <c r="F46" s="11"/>
-      <c r="G46" s="11"/>
-      <c r="H46" s="11"/>
-      <c r="I46" s="11"/>
-      <c r="J46" s="11"/>
-    </row>
-    <row r="47" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B47" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C47" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D47" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E47" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F47" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G47" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="H47" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="I47" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="J47" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E48" s="1">
-        <v>4</v>
-      </c>
-      <c r="F48" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H48" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I48" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E49" s="1">
-        <v>4</v>
-      </c>
-      <c r="F49" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H49" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I49" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" ht="4" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="44" spans="1:10" ht="4" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="A46:J46"/>
+  <mergeCells count="11">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A40:J40"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A30:J30"/>
+    <mergeCell ref="A35:J35"/>
+    <mergeCell ref="A15:J15"/>
+    <mergeCell ref="A20:J20"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A10:J10"/>
-    <mergeCell ref="A41:J41"/>
-    <mergeCell ref="A36:J36"/>
-    <mergeCell ref="A15:J15"/>
-    <mergeCell ref="A31:J31"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A26:J26"/>
-    <mergeCell ref="A21:J21"/>
-    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A25:J25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1848,50 +1851,50 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="23.1796875" customWidth="1"/>
-    <col min="4" max="4" width="16.26953125" customWidth="1"/>
-    <col min="5" max="5" width="25.1796875" customWidth="1"/>
-    <col min="6" max="6" width="20.453125" customWidth="1"/>
-    <col min="7" max="7" width="16.1796875" customWidth="1"/>
-    <col min="11" max="11" width="16.453125" customWidth="1"/>
+    <col min="3" max="3" width="23.1796875" style="11" customWidth="1"/>
+    <col min="4" max="4" width="16.26953125" style="11" customWidth="1"/>
+    <col min="5" max="5" width="25.1796875" style="11" customWidth="1"/>
+    <col min="6" max="6" width="20.453125" style="11" customWidth="1"/>
+    <col min="7" max="7" width="16.1796875" style="11" customWidth="1"/>
+    <col min="11" max="11" width="16.453125" style="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>53</v>
+        <v>88</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>56</v>
+        <v>91</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>57</v>
+        <v>92</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>59</v>
+        <v>94</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
@@ -1958,7 +1961,7 @@
         <v>19</v>
       </c>
       <c r="J3" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K3" s="6" t="s">
         <v>22</v>
@@ -1972,25 +1975,25 @@
         <v>91</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>66</v>
+        <v>21</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>67</v>
+        <v>16</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" s="5">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>31</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J4" s="5">
         <v>3</v>
@@ -2007,28 +2010,28 @@
         <v>89</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>67</v>
+        <v>33</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H5" s="5">
+        <v>29</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="I5" s="5" t="s">
-        <v>28</v>
-      </c>
       <c r="J5" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K5" s="6" t="s">
         <v>22</v>
@@ -2042,28 +2045,28 @@
         <v>741</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="J6" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K6" s="6" t="s">
         <v>22</v>
@@ -2077,25 +2080,25 @@
         <v>240</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="J7" s="5">
         <v>4</v>
@@ -2112,22 +2115,22 @@
         <v>742</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>36</v>
+        <v>9</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>57</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>19</v>
@@ -2147,28 +2150,28 @@
         <v>242</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>37</v>
+        <v>9</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>53</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>19</v>
       </c>
       <c r="J9" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K9" s="6" t="s">
         <v>22</v>
@@ -2191,19 +2194,19 @@
         <v>17</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="I10" s="5" t="s">
         <v>19</v>
       </c>
       <c r="J10" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K10" s="6" t="s">
         <v>22</v>
@@ -2226,13 +2229,13 @@
         <v>24</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="I11" s="5" t="s">
         <v>19</v>
@@ -2252,25 +2255,25 @@
         <v>740</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="J12" s="5">
         <v>4</v>
@@ -2287,28 +2290,28 @@
         <v>239</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="J13" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K13" s="6" t="s">
         <v>22</v>
@@ -2322,28 +2325,28 @@
         <v>731</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>17</v>
+        <v>79</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>19</v>
+        <v>81</v>
       </c>
       <c r="J14" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K14" s="6" t="s">
         <v>22</v>
@@ -2357,28 +2360,28 @@
         <v>228</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="G15" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="H15" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="H15" s="5" t="s">
-        <v>46</v>
-      </c>
       <c r="I15" s="5" t="s">
-        <v>19</v>
+        <v>81</v>
       </c>
       <c r="J15" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K15" s="6" t="s">
         <v>22</v>
@@ -2401,19 +2404,19 @@
         <v>17</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="I16" s="5" t="s">
         <v>19</v>
       </c>
       <c r="J16" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K16" s="6" t="s">
         <v>22</v>
@@ -2436,13 +2439,13 @@
         <v>24</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>19</v>
@@ -2451,76 +2454,6 @@
         <v>4</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A18" s="5">
-        <v>101</v>
-      </c>
-      <c r="B18" s="5">
-        <v>245</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="I18" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="J18" s="5">
-        <v>4</v>
-      </c>
-      <c r="K18" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A19" s="5">
-        <v>101</v>
-      </c>
-      <c r="B19" s="5">
-        <v>744</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="J19" s="5">
-        <v>4</v>
-      </c>
-      <c r="K19" s="6" t="s">
         <v>22</v>
       </c>
     </row>
